--- a/spm/file/23计算机12成绩登分册.xlsx
+++ b/spm/file/23计算机12成绩登分册.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\spm\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61420B83-2411-469F-91EF-FF8A4A71E1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF713CF0-B6CC-4ED7-8F71-52EA4DCBF609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FE57C6A0-A528-4EF9-8913-766B65AD35D3}"/>
   </bookViews>
@@ -1246,7 +1246,7 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1287,93 +1287,6 @@
       <alignment shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1383,6 +1296,94 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1796,102 +1797,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
+      <c r="A1" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
     </row>
     <row r="2" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="36" t="s">
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36" t="s">
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36" t="s">
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="23" t="s">
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="29" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="31"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="22" t="s">
+      <c r="A4" s="37"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="39" t="s">
+      <c r="F4" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="38" t="s">
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="51" t="s">
         <v>141</v>
       </c>
-      <c r="L4" s="23"/>
+      <c r="L4" s="29"/>
     </row>
     <row r="5" spans="1:12" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="31"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="42"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="23"/>
+      <c r="A5" s="37"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="29"/>
     </row>
     <row r="6" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="6" t="s">
@@ -1903,27 +1904,27 @@
       <c r="C6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="47"/>
-      <c r="E6" s="48">
+      <c r="D6" s="18"/>
+      <c r="E6" s="19">
         <v>88</v>
       </c>
-      <c r="F6" s="48">
+      <c r="F6" s="19">
         <v>86</v>
       </c>
-      <c r="G6" s="48">
+      <c r="G6" s="22">
         <v>87.9</v>
       </c>
-      <c r="H6" s="48">
+      <c r="H6" s="19">
         <v>85</v>
       </c>
-      <c r="I6" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="J6" s="47"/>
-      <c r="K6" s="47">
+      <c r="I6" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18">
         <v>2</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="18"/>
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="6" t="s">
@@ -1935,27 +1936,27 @@
       <c r="C7" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="47"/>
-      <c r="E7" s="48">
+      <c r="D7" s="18"/>
+      <c r="E7" s="19">
         <v>88</v>
       </c>
-      <c r="F7" s="48">
+      <c r="F7" s="19">
         <v>70</v>
       </c>
-      <c r="G7" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="H7" s="48">
-        <v>0</v>
-      </c>
-      <c r="I7" s="48">
-        <v>0</v>
-      </c>
-      <c r="J7" s="47"/>
-      <c r="K7" s="47">
+      <c r="G7" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="H7" s="19">
+        <v>0</v>
+      </c>
+      <c r="I7" s="19">
+        <v>0</v>
+      </c>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18">
         <v>1</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="18"/>
     </row>
     <row r="8" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="6" t="s">
@@ -1967,27 +1968,27 @@
       <c r="C8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="47"/>
-      <c r="E8" s="48">
+      <c r="D8" s="18"/>
+      <c r="E8" s="19">
         <v>100</v>
       </c>
-      <c r="F8" s="48">
+      <c r="F8" s="19">
         <v>80</v>
       </c>
-      <c r="G8" s="48">
+      <c r="G8" s="22">
         <v>91.1</v>
       </c>
-      <c r="H8" s="48">
+      <c r="H8" s="19">
         <v>75</v>
       </c>
-      <c r="I8" s="48">
+      <c r="I8" s="19">
         <v>80</v>
       </c>
-      <c r="J8" s="47"/>
-      <c r="K8" s="47">
+      <c r="J8" s="18"/>
+      <c r="K8" s="18">
         <v>8</v>
       </c>
-      <c r="L8" s="47"/>
+      <c r="L8" s="18"/>
     </row>
     <row r="9" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="6" t="s">
@@ -1996,30 +1997,30 @@
       <c r="B9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="50" t="s">
+      <c r="C9" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="D9" s="47"/>
-      <c r="E9" s="48">
+      <c r="D9" s="18"/>
+      <c r="E9" s="19">
         <v>100</v>
       </c>
-      <c r="F9" s="48">
-        <v>0</v>
-      </c>
-      <c r="G9" s="48">
-        <v>0</v>
-      </c>
-      <c r="H9" s="48">
-        <v>0</v>
-      </c>
-      <c r="I9" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="J9" s="47"/>
-      <c r="K9" s="47">
+      <c r="F9" s="19">
+        <v>0</v>
+      </c>
+      <c r="G9" s="22">
+        <v>0</v>
+      </c>
+      <c r="H9" s="19">
+        <v>0</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18">
         <v>1</v>
       </c>
-      <c r="L9" s="47"/>
+      <c r="L9" s="18"/>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="6" t="s">
@@ -2031,27 +2032,27 @@
       <c r="C10" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="47"/>
-      <c r="E10" s="48">
+      <c r="D10" s="18"/>
+      <c r="E10" s="19">
         <v>88</v>
       </c>
-      <c r="F10" s="48">
+      <c r="F10" s="19">
         <v>80</v>
       </c>
-      <c r="G10" s="48">
-        <v>0</v>
-      </c>
-      <c r="H10" s="48">
-        <v>0</v>
-      </c>
-      <c r="I10" s="48">
+      <c r="G10" s="22">
+        <v>0</v>
+      </c>
+      <c r="H10" s="19">
+        <v>0</v>
+      </c>
+      <c r="I10" s="19">
         <v>95</v>
       </c>
-      <c r="J10" s="47"/>
-      <c r="K10" s="47">
+      <c r="J10" s="18"/>
+      <c r="K10" s="18">
         <v>4</v>
       </c>
-      <c r="L10" s="47"/>
+      <c r="L10" s="18"/>
     </row>
     <row r="11" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="6" t="s">
@@ -2063,25 +2064,25 @@
       <c r="C11" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="47"/>
-      <c r="E11" s="48">
+      <c r="D11" s="18"/>
+      <c r="E11" s="19">
         <v>38</v>
       </c>
-      <c r="F11" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="G11" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="H11" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="I11" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="J11" s="47"/>
-      <c r="K11" s="47"/>
-      <c r="L11" s="47"/>
+      <c r="F11" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
     </row>
     <row r="12" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="6" t="s">
@@ -2093,27 +2094,27 @@
       <c r="C12" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="47"/>
-      <c r="E12" s="48">
+      <c r="D12" s="18"/>
+      <c r="E12" s="19">
         <v>100</v>
       </c>
-      <c r="F12" s="48">
+      <c r="F12" s="19">
         <v>80</v>
       </c>
-      <c r="G12" s="48">
+      <c r="G12" s="22">
         <v>94.7</v>
       </c>
-      <c r="H12" s="48">
+      <c r="H12" s="19">
         <v>80</v>
       </c>
-      <c r="I12" s="48">
+      <c r="I12" s="19">
         <v>90</v>
       </c>
-      <c r="J12" s="47"/>
-      <c r="K12" s="47">
+      <c r="J12" s="18"/>
+      <c r="K12" s="18">
         <v>9</v>
       </c>
-      <c r="L12" s="47"/>
+      <c r="L12" s="18"/>
     </row>
     <row r="13" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="6" t="s">
@@ -2125,27 +2126,27 @@
       <c r="C13" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="47"/>
-      <c r="E13" s="48">
+      <c r="D13" s="18"/>
+      <c r="E13" s="19">
         <v>88</v>
       </c>
-      <c r="F13" s="48">
+      <c r="F13" s="19">
         <v>70</v>
       </c>
-      <c r="G13" s="48">
+      <c r="G13" s="22">
         <v>90.1</v>
       </c>
-      <c r="H13" s="48">
+      <c r="H13" s="19">
         <v>85</v>
       </c>
-      <c r="I13" s="48">
-        <v>0</v>
-      </c>
-      <c r="J13" s="47"/>
-      <c r="K13" s="47">
+      <c r="I13" s="19">
+        <v>0</v>
+      </c>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18">
         <v>6</v>
       </c>
-      <c r="L13" s="47"/>
+      <c r="L13" s="18"/>
     </row>
     <row r="14" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="6" t="s">
@@ -2157,27 +2158,27 @@
       <c r="C14" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="47"/>
-      <c r="E14" s="48">
+      <c r="D14" s="18"/>
+      <c r="E14" s="19">
         <v>100</v>
       </c>
-      <c r="F14" s="48">
+      <c r="F14" s="19">
         <v>86</v>
       </c>
-      <c r="G14" s="48">
+      <c r="G14" s="22">
         <v>88.9</v>
       </c>
-      <c r="H14" s="48">
+      <c r="H14" s="19">
         <v>80</v>
       </c>
-      <c r="I14" s="48">
+      <c r="I14" s="19">
         <v>80</v>
       </c>
-      <c r="J14" s="47"/>
-      <c r="K14" s="47">
+      <c r="J14" s="18"/>
+      <c r="K14" s="18">
         <v>3</v>
       </c>
-      <c r="L14" s="47"/>
+      <c r="L14" s="18"/>
     </row>
     <row r="15" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="6" t="s">
@@ -2189,27 +2190,27 @@
       <c r="C15" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="47"/>
-      <c r="E15" s="48">
+      <c r="D15" s="18"/>
+      <c r="E15" s="19">
         <v>100</v>
       </c>
-      <c r="F15" s="48">
+      <c r="F15" s="19">
         <v>88</v>
       </c>
-      <c r="G15" s="48">
+      <c r="G15" s="22">
         <v>98.7</v>
       </c>
-      <c r="H15" s="48">
+      <c r="H15" s="19">
         <v>80</v>
       </c>
-      <c r="I15" s="48">
+      <c r="I15" s="19">
         <v>100</v>
       </c>
-      <c r="J15" s="47"/>
-      <c r="K15" s="47">
+      <c r="J15" s="18"/>
+      <c r="K15" s="18">
         <v>8</v>
       </c>
-      <c r="L15" s="47"/>
+      <c r="L15" s="18"/>
     </row>
     <row r="16" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="6" t="s">
@@ -2221,27 +2222,27 @@
       <c r="C16" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="47"/>
-      <c r="E16" s="48">
+      <c r="D16" s="18"/>
+      <c r="E16" s="19">
         <v>88</v>
       </c>
-      <c r="F16" s="48">
+      <c r="F16" s="19">
         <v>75</v>
       </c>
-      <c r="G16" s="48">
+      <c r="G16" s="22">
         <v>99.4</v>
       </c>
-      <c r="H16" s="48">
+      <c r="H16" s="19">
         <v>80</v>
       </c>
-      <c r="I16" s="48">
+      <c r="I16" s="19">
         <v>75</v>
       </c>
-      <c r="J16" s="47"/>
-      <c r="K16" s="47">
+      <c r="J16" s="18"/>
+      <c r="K16" s="18">
         <v>13</v>
       </c>
-      <c r="L16" s="47"/>
+      <c r="L16" s="18"/>
     </row>
     <row r="17" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="6" t="s">
@@ -2253,27 +2254,27 @@
       <c r="C17" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="47"/>
-      <c r="E17" s="48">
+      <c r="D17" s="18"/>
+      <c r="E17" s="19">
         <v>88</v>
       </c>
-      <c r="F17" s="48">
+      <c r="F17" s="19">
         <v>86</v>
       </c>
-      <c r="G17" s="48">
-        <v>0</v>
-      </c>
-      <c r="H17" s="48">
-        <v>0</v>
-      </c>
-      <c r="I17" s="48">
-        <v>0</v>
-      </c>
-      <c r="J17" s="47"/>
-      <c r="K17" s="47">
+      <c r="G17" s="22">
+        <v>0</v>
+      </c>
+      <c r="H17" s="19">
+        <v>0</v>
+      </c>
+      <c r="I17" s="19">
+        <v>0</v>
+      </c>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18">
         <v>6</v>
       </c>
-      <c r="L17" s="47"/>
+      <c r="L17" s="18"/>
     </row>
     <row r="18" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="6" t="s">
@@ -2285,25 +2286,25 @@
       <c r="C18" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D18" s="47"/>
-      <c r="E18" s="48">
+      <c r="D18" s="18"/>
+      <c r="E18" s="19">
         <v>100</v>
       </c>
-      <c r="F18" s="48">
-        <v>0</v>
-      </c>
-      <c r="G18" s="48">
+      <c r="F18" s="19">
+        <v>0</v>
+      </c>
+      <c r="G18" s="22">
         <v>88.1</v>
       </c>
-      <c r="H18" s="48">
-        <v>0</v>
-      </c>
-      <c r="I18" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="J18" s="47"/>
-      <c r="K18" s="47"/>
-      <c r="L18" s="47"/>
+      <c r="H18" s="19">
+        <v>0</v>
+      </c>
+      <c r="I18" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
     </row>
     <row r="19" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="6" t="s">
@@ -2315,27 +2316,27 @@
       <c r="C19" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D19" s="47"/>
-      <c r="E19" s="48">
+      <c r="D19" s="18"/>
+      <c r="E19" s="19">
         <v>100</v>
       </c>
-      <c r="F19" s="48">
+      <c r="F19" s="19">
         <v>80</v>
       </c>
-      <c r="G19" s="48">
+      <c r="G19" s="22">
         <v>98.7</v>
       </c>
-      <c r="H19" s="48">
+      <c r="H19" s="19">
         <v>88</v>
       </c>
-      <c r="I19" s="48">
+      <c r="I19" s="19">
         <v>100</v>
       </c>
-      <c r="J19" s="47"/>
-      <c r="K19" s="47">
+      <c r="J19" s="18"/>
+      <c r="K19" s="18">
         <v>12</v>
       </c>
-      <c r="L19" s="47"/>
+      <c r="L19" s="18"/>
     </row>
     <row r="20" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="6" t="s">
@@ -2344,30 +2345,30 @@
       <c r="B20" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="50" t="s">
+      <c r="C20" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="D20" s="47"/>
-      <c r="E20" s="48">
+      <c r="D20" s="18"/>
+      <c r="E20" s="19">
         <v>50</v>
       </c>
-      <c r="F20" s="48">
+      <c r="F20" s="19">
         <v>80</v>
       </c>
-      <c r="G20" s="48">
-        <v>0</v>
-      </c>
-      <c r="H20" s="48">
-        <v>0</v>
-      </c>
-      <c r="I20" s="48">
-        <v>0</v>
-      </c>
-      <c r="J20" s="47"/>
-      <c r="K20" s="47">
+      <c r="G20" s="22">
+        <v>0</v>
+      </c>
+      <c r="H20" s="19">
+        <v>0</v>
+      </c>
+      <c r="I20" s="19">
+        <v>0</v>
+      </c>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18">
         <v>1</v>
       </c>
-      <c r="L20" s="47"/>
+      <c r="L20" s="18"/>
     </row>
     <row r="21" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="6" t="s">
@@ -2379,25 +2380,25 @@
       <c r="C21" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="47"/>
-      <c r="E21" s="48">
+      <c r="D21" s="18"/>
+      <c r="E21" s="19">
         <v>63</v>
       </c>
-      <c r="F21" s="48">
-        <v>0</v>
-      </c>
-      <c r="G21" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="H21" s="48">
+      <c r="F21" s="19">
+        <v>0</v>
+      </c>
+      <c r="G21" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="H21" s="19">
         <v>60</v>
       </c>
-      <c r="I21" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="J21" s="47"/>
-      <c r="K21" s="47"/>
-      <c r="L21" s="47"/>
+      <c r="I21" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
     </row>
     <row r="22" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="6" t="s">
@@ -2409,25 +2410,25 @@
       <c r="C22" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D22" s="47"/>
-      <c r="E22" s="48">
+      <c r="D22" s="18"/>
+      <c r="E22" s="19">
         <v>75</v>
       </c>
-      <c r="F22" s="48">
-        <v>0</v>
-      </c>
-      <c r="G22" s="48">
-        <v>0</v>
-      </c>
-      <c r="H22" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="I22" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="J22" s="47"/>
-      <c r="K22" s="47"/>
-      <c r="L22" s="47"/>
+      <c r="F22" s="19">
+        <v>0</v>
+      </c>
+      <c r="G22" s="22">
+        <v>0</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="I22" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
     </row>
     <row r="23" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="6" t="s">
@@ -2439,27 +2440,27 @@
       <c r="C23" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D23" s="47"/>
-      <c r="E23" s="48">
+      <c r="D23" s="18"/>
+      <c r="E23" s="19">
         <v>50</v>
       </c>
-      <c r="F23" s="48">
+      <c r="F23" s="19">
         <v>85</v>
       </c>
-      <c r="G23" s="48">
+      <c r="G23" s="22">
         <v>90.2</v>
       </c>
-      <c r="H23" s="48">
-        <v>0</v>
-      </c>
-      <c r="I23" s="48">
-        <v>0</v>
-      </c>
-      <c r="J23" s="47"/>
-      <c r="K23" s="47">
+      <c r="H23" s="19">
+        <v>0</v>
+      </c>
+      <c r="I23" s="19">
+        <v>0</v>
+      </c>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18">
         <v>2</v>
       </c>
-      <c r="L23" s="47"/>
+      <c r="L23" s="18"/>
     </row>
     <row r="24" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="6" t="s">
@@ -2468,30 +2469,30 @@
       <c r="B24" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C24" s="50" t="s">
+      <c r="C24" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="D24" s="47"/>
-      <c r="E24" s="48">
+      <c r="D24" s="18"/>
+      <c r="E24" s="19">
         <v>100</v>
       </c>
-      <c r="F24" s="48">
+      <c r="F24" s="19">
         <v>86</v>
       </c>
-      <c r="G24" s="48">
+      <c r="G24" s="22">
         <v>92.2</v>
       </c>
-      <c r="H24" s="48">
+      <c r="H24" s="19">
         <v>85</v>
       </c>
-      <c r="I24" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="J24" s="47"/>
-      <c r="K24" s="47">
+      <c r="I24" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18">
         <v>2</v>
       </c>
-      <c r="L24" s="47"/>
+      <c r="L24" s="18"/>
     </row>
     <row r="25" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="6" t="s">
@@ -2503,27 +2504,27 @@
       <c r="C25" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="D25" s="47"/>
-      <c r="E25" s="48">
+      <c r="D25" s="18"/>
+      <c r="E25" s="19">
         <v>88</v>
       </c>
-      <c r="F25" s="48">
-        <v>0</v>
-      </c>
-      <c r="G25" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="H25" s="48">
+      <c r="F25" s="19">
+        <v>0</v>
+      </c>
+      <c r="G25" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="H25" s="19">
         <v>70</v>
       </c>
-      <c r="I25" s="48">
-        <v>0</v>
-      </c>
-      <c r="J25" s="47"/>
-      <c r="K25" s="47">
+      <c r="I25" s="19">
+        <v>0</v>
+      </c>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18">
         <v>2</v>
       </c>
-      <c r="L25" s="47"/>
+      <c r="L25" s="18"/>
     </row>
     <row r="26" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="6" t="s">
@@ -2535,25 +2536,25 @@
       <c r="C26" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D26" s="47"/>
-      <c r="E26" s="48">
+      <c r="D26" s="18"/>
+      <c r="E26" s="19">
         <v>100</v>
       </c>
-      <c r="F26" s="48">
-        <v>0</v>
-      </c>
-      <c r="G26" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="H26" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="I26" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="J26" s="47"/>
-      <c r="K26" s="47"/>
-      <c r="L26" s="47"/>
+      <c r="F26" s="19">
+        <v>0</v>
+      </c>
+      <c r="G26" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="H26" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="I26" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
     </row>
     <row r="27" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="6" t="s">
@@ -2565,25 +2566,25 @@
       <c r="C27" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="47"/>
-      <c r="E27" s="48">
+      <c r="D27" s="18"/>
+      <c r="E27" s="19">
         <v>25</v>
       </c>
-      <c r="F27" s="48">
-        <v>0</v>
-      </c>
-      <c r="G27" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="H27" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="I27" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="J27" s="47"/>
-      <c r="K27" s="47"/>
-      <c r="L27" s="47"/>
+      <c r="F27" s="19">
+        <v>0</v>
+      </c>
+      <c r="G27" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="H27" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="I27" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
     </row>
     <row r="28" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="6" t="s">
@@ -2595,25 +2596,25 @@
       <c r="C28" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="D28" s="47"/>
-      <c r="E28" s="48">
+      <c r="D28" s="18"/>
+      <c r="E28" s="19">
         <v>88</v>
       </c>
-      <c r="F28" s="48">
+      <c r="F28" s="19">
         <v>88</v>
       </c>
-      <c r="G28" s="48">
+      <c r="G28" s="22">
         <v>87.2</v>
       </c>
-      <c r="H28" s="48">
+      <c r="H28" s="19">
         <v>75</v>
       </c>
-      <c r="I28" s="48">
+      <c r="I28" s="19">
         <v>80</v>
       </c>
-      <c r="J28" s="47"/>
-      <c r="K28" s="47"/>
-      <c r="L28" s="47"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
     </row>
     <row r="29" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="6" t="s">
@@ -2625,25 +2626,25 @@
       <c r="C29" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D29" s="47"/>
-      <c r="E29" s="48">
+      <c r="D29" s="18"/>
+      <c r="E29" s="19">
         <v>63</v>
       </c>
-      <c r="F29" s="48">
-        <v>0</v>
-      </c>
-      <c r="G29" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="H29" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="I29" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="J29" s="47"/>
-      <c r="K29" s="47"/>
-      <c r="L29" s="47"/>
+      <c r="F29" s="19">
+        <v>0</v>
+      </c>
+      <c r="G29" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="I29" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J29" s="18"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="18"/>
     </row>
     <row r="30" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="6" t="s">
@@ -2655,25 +2656,25 @@
       <c r="C30" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="D30" s="47"/>
-      <c r="E30" s="48">
+      <c r="D30" s="18"/>
+      <c r="E30" s="19">
         <v>75</v>
       </c>
-      <c r="F30" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="G30" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="H30" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="I30" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="J30" s="47"/>
-      <c r="K30" s="47"/>
-      <c r="L30" s="47"/>
+      <c r="F30" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="G30" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="H30" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="I30" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J30" s="18"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="18"/>
     </row>
     <row r="31" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="6" t="s">
@@ -2685,25 +2686,25 @@
       <c r="C31" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="D31" s="47"/>
-      <c r="E31" s="48">
+      <c r="D31" s="18"/>
+      <c r="E31" s="19">
         <v>75</v>
       </c>
-      <c r="F31" s="48">
-        <v>0</v>
-      </c>
-      <c r="G31" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="H31" s="48">
-        <v>0</v>
-      </c>
-      <c r="I31" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="J31" s="47"/>
-      <c r="K31" s="47"/>
-      <c r="L31" s="47"/>
+      <c r="F31" s="19">
+        <v>0</v>
+      </c>
+      <c r="G31" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="H31" s="19">
+        <v>0</v>
+      </c>
+      <c r="I31" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J31" s="18"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
     </row>
     <row r="32" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="6" t="s">
@@ -2715,25 +2716,25 @@
       <c r="C32" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D32" s="47"/>
-      <c r="E32" s="48">
+      <c r="D32" s="18"/>
+      <c r="E32" s="19">
         <v>88</v>
       </c>
-      <c r="F32" s="48">
-        <v>0</v>
-      </c>
-      <c r="G32" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="H32" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="I32" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="J32" s="47"/>
-      <c r="K32" s="47"/>
-      <c r="L32" s="47"/>
+      <c r="F32" s="19">
+        <v>0</v>
+      </c>
+      <c r="G32" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="I32" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
     </row>
     <row r="33" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="6" t="s">
@@ -2745,27 +2746,27 @@
       <c r="C33" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="D33" s="47"/>
-      <c r="E33" s="48">
+      <c r="D33" s="18"/>
+      <c r="E33" s="19">
         <v>88</v>
       </c>
-      <c r="F33" s="48">
+      <c r="F33" s="19">
         <v>80</v>
       </c>
-      <c r="G33" s="48">
+      <c r="G33" s="22">
         <v>74.5</v>
       </c>
-      <c r="H33" s="48">
+      <c r="H33" s="19">
         <v>75</v>
       </c>
-      <c r="I33" s="48">
-        <v>0</v>
-      </c>
-      <c r="J33" s="47"/>
-      <c r="K33" s="47">
+      <c r="I33" s="19">
+        <v>0</v>
+      </c>
+      <c r="J33" s="18"/>
+      <c r="K33" s="18">
         <v>1</v>
       </c>
-      <c r="L33" s="47"/>
+      <c r="L33" s="18"/>
     </row>
     <row r="34" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="6" t="s">
@@ -2777,25 +2778,25 @@
       <c r="C34" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D34" s="47"/>
-      <c r="E34" s="48">
+      <c r="D34" s="18"/>
+      <c r="E34" s="19">
         <v>63</v>
       </c>
-      <c r="F34" s="48">
+      <c r="F34" s="19">
         <v>70</v>
       </c>
-      <c r="G34" s="48">
-        <v>0</v>
-      </c>
-      <c r="H34" s="48">
+      <c r="G34" s="22">
+        <v>0</v>
+      </c>
+      <c r="H34" s="19">
         <v>60</v>
       </c>
-      <c r="I34" s="48">
+      <c r="I34" s="19">
         <v>95</v>
       </c>
-      <c r="J34" s="47"/>
-      <c r="K34" s="47"/>
-      <c r="L34" s="47"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
     </row>
     <row r="35" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="6" t="s">
@@ -2807,25 +2808,25 @@
       <c r="C35" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="D35" s="47"/>
-      <c r="E35" s="48">
+      <c r="D35" s="18"/>
+      <c r="E35" s="19">
         <v>75</v>
       </c>
-      <c r="F35" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="G35" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="H35" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="I35" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="J35" s="47"/>
-      <c r="K35" s="47"/>
-      <c r="L35" s="47"/>
+      <c r="F35" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="G35" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="H35" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="I35" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
     </row>
     <row r="36" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="6" t="s">
@@ -2837,27 +2838,27 @@
       <c r="C36" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="D36" s="47"/>
-      <c r="E36" s="48">
+      <c r="D36" s="18"/>
+      <c r="E36" s="19">
         <v>88</v>
       </c>
-      <c r="F36" s="48">
+      <c r="F36" s="19">
         <v>88</v>
       </c>
-      <c r="G36" s="48">
+      <c r="G36" s="22">
         <v>93.2</v>
       </c>
-      <c r="H36" s="48">
+      <c r="H36" s="19">
         <v>88</v>
       </c>
-      <c r="I36" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="J36" s="47"/>
-      <c r="K36" s="47">
+      <c r="I36" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J36" s="18"/>
+      <c r="K36" s="18">
         <v>4</v>
       </c>
-      <c r="L36" s="47"/>
+      <c r="L36" s="18"/>
     </row>
     <row r="37" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="6" t="s">
@@ -2869,25 +2870,25 @@
       <c r="C37" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="D37" s="47"/>
-      <c r="E37" s="48">
+      <c r="D37" s="18"/>
+      <c r="E37" s="19">
         <v>75</v>
       </c>
-      <c r="F37" s="48">
+      <c r="F37" s="19">
         <v>85</v>
       </c>
-      <c r="G37" s="48">
+      <c r="G37" s="22">
         <v>96.4</v>
       </c>
-      <c r="H37" s="48">
+      <c r="H37" s="19">
         <v>80</v>
       </c>
-      <c r="I37" s="48">
-        <v>0</v>
-      </c>
-      <c r="J37" s="47"/>
-      <c r="K37" s="47"/>
-      <c r="L37" s="47"/>
+      <c r="I37" s="19">
+        <v>0</v>
+      </c>
+      <c r="J37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
     </row>
     <row r="38" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="6" t="s">
@@ -2899,25 +2900,25 @@
       <c r="C38" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="D38" s="47"/>
-      <c r="E38" s="48">
+      <c r="D38" s="18"/>
+      <c r="E38" s="19">
         <v>88</v>
       </c>
-      <c r="F38" s="48">
+      <c r="F38" s="19">
         <v>80</v>
       </c>
-      <c r="G38" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="H38" s="48">
+      <c r="G38" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="H38" s="19">
         <v>80</v>
       </c>
-      <c r="I38" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="J38" s="47"/>
-      <c r="K38" s="47"/>
-      <c r="L38" s="47"/>
+      <c r="I38" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
     </row>
     <row r="39" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="6" t="s">
@@ -2929,25 +2930,25 @@
       <c r="C39" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="D39" s="47"/>
-      <c r="E39" s="48">
+      <c r="D39" s="18"/>
+      <c r="E39" s="19">
         <v>100</v>
       </c>
-      <c r="F39" s="48">
-        <v>0</v>
-      </c>
-      <c r="G39" s="48">
+      <c r="F39" s="19">
+        <v>0</v>
+      </c>
+      <c r="G39" s="22">
         <v>63.1</v>
       </c>
-      <c r="H39" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="I39" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="J39" s="47"/>
-      <c r="K39" s="47"/>
-      <c r="L39" s="47"/>
+      <c r="H39" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="I39" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
     </row>
     <row r="40" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="6" t="s">
@@ -2959,27 +2960,27 @@
       <c r="C40" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="D40" s="47"/>
-      <c r="E40" s="48">
+      <c r="D40" s="18"/>
+      <c r="E40" s="19">
         <v>100</v>
       </c>
-      <c r="F40" s="48">
+      <c r="F40" s="19">
         <v>99</v>
       </c>
-      <c r="G40" s="48">
+      <c r="G40" s="22">
         <v>83</v>
       </c>
-      <c r="H40" s="48">
+      <c r="H40" s="19">
         <v>80</v>
       </c>
-      <c r="I40" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="J40" s="47"/>
-      <c r="K40" s="47">
+      <c r="I40" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="J40" s="18"/>
+      <c r="K40" s="18">
         <v>10</v>
       </c>
-      <c r="L40" s="47"/>
+      <c r="L40" s="18"/>
     </row>
     <row r="41" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="6" t="s">
@@ -2991,27 +2992,27 @@
       <c r="C41" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="D41" s="47"/>
-      <c r="E41" s="48">
+      <c r="D41" s="18"/>
+      <c r="E41" s="19">
         <v>88</v>
       </c>
-      <c r="F41" s="48">
+      <c r="F41" s="19">
         <v>95</v>
       </c>
-      <c r="G41" s="48">
+      <c r="G41" s="22">
         <v>80.7</v>
       </c>
-      <c r="H41" s="48">
+      <c r="H41" s="19">
         <v>88</v>
       </c>
-      <c r="I41" s="48">
+      <c r="I41" s="19">
         <v>90</v>
       </c>
-      <c r="J41" s="47"/>
-      <c r="K41" s="47">
+      <c r="J41" s="18"/>
+      <c r="K41" s="18">
         <v>7</v>
       </c>
-      <c r="L41" s="47"/>
+      <c r="L41" s="18"/>
     </row>
     <row r="42" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="6" t="s">
@@ -3023,27 +3024,27 @@
       <c r="C42" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="D42" s="47"/>
-      <c r="E42" s="48">
+      <c r="D42" s="18"/>
+      <c r="E42" s="19">
         <v>88</v>
       </c>
-      <c r="F42" s="48">
+      <c r="F42" s="19">
         <v>86</v>
       </c>
-      <c r="G42" s="48">
+      <c r="G42" s="22">
         <v>93.5</v>
       </c>
-      <c r="H42" s="48">
+      <c r="H42" s="19">
         <v>70</v>
       </c>
-      <c r="I42" s="48">
-        <v>0</v>
-      </c>
-      <c r="J42" s="47"/>
-      <c r="K42" s="47">
+      <c r="I42" s="19">
+        <v>0</v>
+      </c>
+      <c r="J42" s="18"/>
+      <c r="K42" s="18">
         <v>9</v>
       </c>
-      <c r="L42" s="47"/>
+      <c r="L42" s="18"/>
     </row>
     <row r="43" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="6" t="s">
@@ -3055,27 +3056,27 @@
       <c r="C43" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D43" s="47"/>
-      <c r="E43" s="48">
+      <c r="D43" s="18"/>
+      <c r="E43" s="19">
         <v>88</v>
       </c>
-      <c r="F43" s="48">
+      <c r="F43" s="19">
         <v>88</v>
       </c>
-      <c r="G43" s="48">
+      <c r="G43" s="22">
         <v>84.3</v>
       </c>
-      <c r="H43" s="48">
+      <c r="H43" s="19">
         <v>85</v>
       </c>
-      <c r="I43" s="48">
+      <c r="I43" s="19">
         <v>90</v>
       </c>
-      <c r="J43" s="47"/>
-      <c r="K43" s="47">
+      <c r="J43" s="18"/>
+      <c r="K43" s="18">
         <v>11</v>
       </c>
-      <c r="L43" s="47"/>
+      <c r="L43" s="18"/>
     </row>
     <row r="44" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="6" t="s">
@@ -3087,52 +3088,52 @@
       <c r="C44" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="D44" s="47"/>
-      <c r="E44" s="48">
+      <c r="D44" s="18"/>
+      <c r="E44" s="19">
         <v>88</v>
       </c>
-      <c r="F44" s="48">
+      <c r="F44" s="19">
         <v>85</v>
       </c>
-      <c r="G44" s="48">
+      <c r="G44" s="22">
         <v>78.7</v>
       </c>
-      <c r="H44" s="48">
+      <c r="H44" s="19">
         <v>88</v>
       </c>
-      <c r="I44" s="48">
+      <c r="I44" s="19">
         <v>100</v>
       </c>
-      <c r="J44" s="47"/>
-      <c r="K44" s="47">
+      <c r="J44" s="18"/>
+      <c r="K44" s="18">
         <v>5</v>
       </c>
-      <c r="L44" s="47"/>
+      <c r="L44" s="18"/>
     </row>
     <row r="45" spans="1:12" s="3" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="B46" s="24" t="s">
+      <c r="B46" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="C46" s="24"/>
-      <c r="D46" s="24"/>
-      <c r="E46" s="24"/>
-      <c r="F46" s="24"/>
-      <c r="G46" s="24"/>
-      <c r="H46" s="24"/>
-      <c r="I46" s="24"/>
-      <c r="J46" s="24"/>
-      <c r="K46" s="24"/>
-      <c r="L46" s="24"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A47" s="25" t="s">
+      <c r="A47" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="B47" s="26"/>
+      <c r="B47" s="32"/>
       <c r="C47" s="12" t="s">
         <v>11</v>
       </c>
@@ -3148,29 +3149,29 @@
       <c r="G47" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="H47" s="25" t="s">
+      <c r="H47" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="I47" s="27"/>
-      <c r="J47" s="26"/>
-      <c r="K47" s="28" t="s">
+      <c r="I47" s="33"/>
+      <c r="J47" s="32"/>
+      <c r="K47" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="L47" s="29"/>
+      <c r="L47" s="35"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A48" s="18"/>
-      <c r="B48" s="18"/>
+      <c r="A48" s="23"/>
+      <c r="B48" s="23"/>
       <c r="C48" s="13"/>
       <c r="D48" s="13"/>
       <c r="E48" s="13"/>
       <c r="F48" s="14"/>
       <c r="G48" s="14"/>
-      <c r="H48" s="19"/>
-      <c r="I48" s="20"/>
-      <c r="J48" s="21"/>
-      <c r="K48" s="19"/>
-      <c r="L48" s="21"/>
+      <c r="H48" s="24"/>
+      <c r="I48" s="25"/>
+      <c r="J48" s="26"/>
+      <c r="K48" s="24"/>
+      <c r="L48" s="26"/>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -3188,102 +3189,102 @@
       <c r="L51" s="17"/>
     </row>
     <row r="53" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="B53" s="34"/>
-      <c r="C53" s="34"/>
-      <c r="D53" s="34"/>
-      <c r="E53" s="34"/>
-      <c r="F53" s="34"/>
-      <c r="G53" s="34"/>
-      <c r="H53" s="34"/>
-      <c r="I53" s="34"/>
-      <c r="J53" s="34"/>
-      <c r="K53" s="34"/>
-      <c r="L53" s="34"/>
+      <c r="A53" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="B53" s="43"/>
+      <c r="C53" s="43"/>
+      <c r="D53" s="43"/>
+      <c r="E53" s="43"/>
+      <c r="F53" s="43"/>
+      <c r="G53" s="43"/>
+      <c r="H53" s="43"/>
+      <c r="I53" s="43"/>
+      <c r="J53" s="43"/>
+      <c r="K53" s="43"/>
+      <c r="L53" s="43"/>
     </row>
     <row r="54" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="35" t="s">
+      <c r="A54" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="B54" s="35"/>
-      <c r="C54" s="35"/>
-      <c r="D54" s="36" t="s">
+      <c r="B54" s="41"/>
+      <c r="C54" s="41"/>
+      <c r="D54" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="E54" s="36"/>
-      <c r="F54" s="36"/>
-      <c r="G54" s="36" t="s">
+      <c r="E54" s="42"/>
+      <c r="F54" s="42"/>
+      <c r="G54" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="H54" s="36"/>
-      <c r="I54" s="36"/>
-      <c r="J54" s="36" t="s">
+      <c r="H54" s="42"/>
+      <c r="I54" s="42"/>
+      <c r="J54" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="K54" s="36"/>
-      <c r="L54" s="36"/>
+      <c r="K54" s="42"/>
+      <c r="L54" s="42"/>
     </row>
     <row r="55" spans="1:12" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="31" t="s">
+      <c r="A55" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B55" s="32" t="s">
+      <c r="B55" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="C55" s="33" t="s">
+      <c r="C55" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="D55" s="30" t="s">
+      <c r="D55" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="E55" s="30"/>
-      <c r="F55" s="30"/>
-      <c r="G55" s="30"/>
-      <c r="H55" s="30"/>
-      <c r="I55" s="30"/>
-      <c r="J55" s="30"/>
-      <c r="K55" s="30"/>
-      <c r="L55" s="23" t="s">
+      <c r="E55" s="36"/>
+      <c r="F55" s="36"/>
+      <c r="G55" s="36"/>
+      <c r="H55" s="36"/>
+      <c r="I55" s="36"/>
+      <c r="J55" s="36"/>
+      <c r="K55" s="36"/>
+      <c r="L55" s="29" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:12" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="31"/>
-      <c r="B56" s="32"/>
-      <c r="C56" s="33"/>
-      <c r="D56" s="22" t="s">
+      <c r="A56" s="37"/>
+      <c r="B56" s="38"/>
+      <c r="C56" s="39"/>
+      <c r="D56" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="E56" s="22" t="s">
+      <c r="E56" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="F56" s="39" t="s">
+      <c r="F56" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="G56" s="40"/>
-      <c r="H56" s="40"/>
-      <c r="I56" s="40"/>
-      <c r="J56" s="41"/>
-      <c r="K56" s="45" t="s">
+      <c r="G56" s="45"/>
+      <c r="H56" s="45"/>
+      <c r="I56" s="45"/>
+      <c r="J56" s="46"/>
+      <c r="K56" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="L56" s="23"/>
+      <c r="L56" s="29"/>
     </row>
     <row r="57" spans="1:12" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="31"/>
-      <c r="B57" s="32"/>
-      <c r="C57" s="33"/>
-      <c r="D57" s="22"/>
-      <c r="E57" s="37"/>
-      <c r="F57" s="43"/>
-      <c r="G57" s="44"/>
-      <c r="H57" s="44"/>
-      <c r="I57" s="44"/>
-      <c r="J57" s="46"/>
-      <c r="K57" s="22"/>
-      <c r="L57" s="23"/>
+      <c r="A57" s="37"/>
+      <c r="B57" s="38"/>
+      <c r="C57" s="39"/>
+      <c r="D57" s="28"/>
+      <c r="E57" s="40"/>
+      <c r="F57" s="47"/>
+      <c r="G57" s="48"/>
+      <c r="H57" s="48"/>
+      <c r="I57" s="48"/>
+      <c r="J57" s="50"/>
+      <c r="K57" s="28"/>
+      <c r="L57" s="29"/>
     </row>
     <row r="58" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="6" t="s">
@@ -3296,49 +3297,49 @@
         <v>140</v>
       </c>
       <c r="D58" s="9"/>
-      <c r="E58" s="48">
+      <c r="E58" s="19">
         <v>13</v>
       </c>
-      <c r="F58" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="G58" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="H58" s="48">
-        <v>0</v>
-      </c>
-      <c r="I58" s="48">
-        <v>0</v>
-      </c>
-      <c r="J58" s="49"/>
-      <c r="K58" s="47"/>
-      <c r="L58" s="47"/>
+      <c r="F58" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="G58" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="H58" s="19">
+        <v>0</v>
+      </c>
+      <c r="I58" s="19">
+        <v>0</v>
+      </c>
+      <c r="J58" s="20"/>
+      <c r="K58" s="18"/>
+      <c r="L58" s="18"/>
     </row>
     <row r="59" spans="1:12" s="3" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="B59" s="10"/>
       <c r="C59" s="11"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="B60" s="24" t="s">
+      <c r="B60" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="C60" s="24"/>
-      <c r="D60" s="24"/>
-      <c r="E60" s="24"/>
-      <c r="F60" s="24"/>
-      <c r="G60" s="24"/>
-      <c r="H60" s="24"/>
-      <c r="I60" s="24"/>
-      <c r="J60" s="24"/>
-      <c r="K60" s="24"/>
-      <c r="L60" s="24"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="30"/>
+      <c r="E60" s="30"/>
+      <c r="F60" s="30"/>
+      <c r="G60" s="30"/>
+      <c r="H60" s="30"/>
+      <c r="I60" s="30"/>
+      <c r="J60" s="30"/>
+      <c r="K60" s="30"/>
+      <c r="L60" s="30"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A61" s="25" t="s">
+      <c r="A61" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="B61" s="26"/>
+      <c r="B61" s="32"/>
       <c r="C61" s="12" t="s">
         <v>11</v>
       </c>
@@ -3354,29 +3355,29 @@
       <c r="G61" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="H61" s="25" t="s">
+      <c r="H61" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="I61" s="27"/>
-      <c r="J61" s="26"/>
-      <c r="K61" s="28" t="s">
+      <c r="I61" s="33"/>
+      <c r="J61" s="32"/>
+      <c r="K61" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="L61" s="29"/>
+      <c r="L61" s="35"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A62" s="18"/>
-      <c r="B62" s="18"/>
+      <c r="A62" s="23"/>
+      <c r="B62" s="23"/>
       <c r="C62" s="13"/>
       <c r="D62" s="13"/>
       <c r="E62" s="13"/>
       <c r="F62" s="14"/>
       <c r="G62" s="14"/>
-      <c r="H62" s="19"/>
-      <c r="I62" s="20"/>
-      <c r="J62" s="21"/>
-      <c r="K62" s="19"/>
-      <c r="L62" s="21"/>
+      <c r="H62" s="24"/>
+      <c r="I62" s="25"/>
+      <c r="J62" s="26"/>
+      <c r="K62" s="24"/>
+      <c r="L62" s="26"/>
     </row>
     <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -3395,14 +3396,18 @@
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:J5"/>
-    <mergeCell ref="F56:J57"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="K48:L48"/>
+    <mergeCell ref="A53:L53"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:J5"/>
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="L3:L5"/>
     <mergeCell ref="B46:L46"/>
@@ -3411,11 +3416,6 @@
     <mergeCell ref="K47:L47"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="D3:K3"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="K48:L48"/>
-    <mergeCell ref="A53:L53"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="D54:F54"/>
     <mergeCell ref="G54:I54"/>
@@ -3437,6 +3437,7 @@
     <mergeCell ref="C55:C57"/>
     <mergeCell ref="D56:D57"/>
     <mergeCell ref="E56:E57"/>
+    <mergeCell ref="F56:J57"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.11805555555555555" right="0.11805555555555555" top="0.38124999999999998" bottom="0.5" header="0.38124999999999998" footer="0.5"/>
